--- a/ig/main/StructureDefinition-as-ext-healthcareservice-authorization.xlsx
+++ b/ig/main/StructureDefinition-as-ext-healthcareservice-authorization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-18T12:23:29+00:00</t>
+    <t>2023-12-18T12:24:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-ext-healthcareservice-authorization.xlsx
+++ b/ig/main/StructureDefinition-as-ext-healthcareservice-authorization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-18T12:24:31+00:00</t>
+    <t>2023-12-18T13:29:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-ext-healthcareservice-authorization.xlsx
+++ b/ig/main/StructureDefinition-as-ext-healthcareservice-authorization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-18T13:29:44+00:00</t>
+    <t>2023-12-19T08:36:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-ext-healthcareservice-authorization.xlsx
+++ b/ig/main/StructureDefinition-as-ext-healthcareservice-authorization.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0-ballot-2</t>
+    <t>1.0.0-ballot-3</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-19T08:36:38+00:00</t>
+    <t>2023-12-19T15:11:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-ext-healthcareservice-authorization.xlsx
+++ b/ig/main/StructureDefinition-as-ext-healthcareservice-authorization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-19T15:11:46+00:00</t>
+    <t>2023-12-21T16:59:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-ext-healthcareservice-authorization.xlsx
+++ b/ig/main/StructureDefinition-as-ext-healthcareservice-authorization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T16:59:47+00:00</t>
+    <t>2024-01-11T15:09:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-ext-healthcareservice-authorization.xlsx
+++ b/ig/main/StructureDefinition-as-ext-healthcareservice-authorization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-11T15:09:13+00:00</t>
+    <t>2024-02-05T18:22:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -597,7 +597,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_R301-SourceInformationInstallation/FHIR/TRE-R301-SourceInformationInstallation</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/ValueSet/as-vs-source-information-installation</t>
   </si>
   <si>
     <t>base64Binary
@@ -939,7 +939,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="21.57421875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="109.89453125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="85.83984375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>

--- a/ig/main/StructureDefinition-as-ext-healthcareservice-authorization.xlsx
+++ b/ig/main/StructureDefinition-as-ext-healthcareservice-authorization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-05T18:22:24+00:00</t>
+    <t>2024-02-05T18:22:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-ext-healthcareservice-authorization.xlsx
+++ b/ig/main/StructureDefinition-as-ext-healthcareservice-authorization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-05T18:22:48+00:00</t>
+    <t>2024-02-05T18:23:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-ext-healthcareservice-authorization.xlsx
+++ b/ig/main/StructureDefinition-as-ext-healthcareservice-authorization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-05T18:23:38+00:00</t>
+    <t>2024-02-07T08:22:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-ext-healthcareservice-authorization.xlsx
+++ b/ig/main/StructureDefinition-as-ext-healthcareservice-authorization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-07T08:22:38+00:00</t>
+    <t>2024-02-08T15:43:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-ext-healthcareservice-authorization.xlsx
+++ b/ig/main/StructureDefinition-as-ext-healthcareservice-authorization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-08T15:43:07+00:00</t>
+    <t>2024-02-08T15:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-ext-healthcareservice-authorization.xlsx
+++ b/ig/main/StructureDefinition-as-ext-healthcareservice-authorization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-08T15:45:12+00:00</t>
+    <t>2024-02-16T10:46:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-ext-healthcareservice-authorization.xlsx
+++ b/ig/main/StructureDefinition-as-ext-healthcareservice-authorization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-16T10:46:50+00:00</t>
+    <t>2024-02-16T10:57:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-as-ext-healthcareservice-authorization.xlsx
+++ b/ig/main/StructureDefinition-as-ext-healthcareservice-authorization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-16T10:57:00+00:00</t>
+    <t>2024-02-16T18:38:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
